--- a/data/trans_dic/POLIPATOLOGIA_2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas</t>
+          <t>Población con dos o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,39; 23,28</t>
+          <t>14,35; 23,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,24; 28,5</t>
+          <t>18,15; 28,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,5; 29,93</t>
+          <t>19,86; 30,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,73; 34,05</t>
+          <t>22,97; 34,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,66; 31,5</t>
+          <t>20,41; 31,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,07; 47,1</t>
+          <t>35,12; 48,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,76; 47,61</t>
+          <t>35,54; 47,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,54; 38,39</t>
+          <t>29,33; 38,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,61; 25,47</t>
+          <t>18,38; 25,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,34; 36,33</t>
+          <t>28,01; 36,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,02; 36,95</t>
+          <t>29,11; 36,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,18; 34,93</t>
+          <t>27,43; 34,52</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,61; 21,72</t>
+          <t>15,14; 22,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,29; 25,18</t>
+          <t>17,66; 25,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,08; 25,28</t>
+          <t>18,48; 26,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,66; 30,78</t>
+          <t>21,31; 30,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,21; 44,92</t>
+          <t>36,3; 44,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,72; 38,77</t>
+          <t>30,12; 39,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,94; 39,59</t>
+          <t>31,18; 39,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,84; 43,57</t>
+          <t>36,37; 43,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,56; 32,4</t>
+          <t>26,53; 32,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,83; 31,1</t>
+          <t>25,21; 30,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,71; 31,75</t>
+          <t>25,9; 31,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,81; 36,07</t>
+          <t>29,74; 35,8</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,9; 20,97</t>
+          <t>12,97; 21,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,97; 33,29</t>
+          <t>22,95; 33,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,9; 23,51</t>
+          <t>15,12; 23,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,73; 41,06</t>
+          <t>30,86; 40,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,79; 35,95</t>
+          <t>25,42; 35,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,32; 41,83</t>
+          <t>31,34; 42,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,83; 37,14</t>
+          <t>27,35; 37,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,18; 51,41</t>
+          <t>42,51; 51,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,78; 27,25</t>
+          <t>20,52; 27,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,45; 36,02</t>
+          <t>29,11; 36,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,47; 29,1</t>
+          <t>22,27; 29,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,3; 45,09</t>
+          <t>37,9; 44,59</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,41; 25,05</t>
+          <t>17,36; 25,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,48; 28,76</t>
+          <t>19,19; 28,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,32; 34,52</t>
+          <t>24,03; 33,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,91; 42,48</t>
+          <t>29,48; 41,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,33; 36,0</t>
+          <t>26,05; 35,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,97; 49,48</t>
+          <t>39,0; 49,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,78; 48,09</t>
+          <t>37,48; 47,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,53; 70,9</t>
+          <t>41,36; 71,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,73; 28,79</t>
+          <t>22,76; 29,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,57; 37,7</t>
+          <t>30,39; 37,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32,22; 39,52</t>
+          <t>32,45; 40,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38,75; 62,33</t>
+          <t>38,91; 59,85</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 18,09</t>
+          <t>8,5; 17,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,38; 35,07</t>
+          <t>21,88; 34,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,32; 28,88</t>
+          <t>17,33; 28,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,82; 38,94</t>
+          <t>28,14; 39,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,98; 37,78</t>
+          <t>24,29; 37,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,71; 65,49</t>
+          <t>52,73; 66,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,89; 46,72</t>
+          <t>34,58; 46,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,32; 55,12</t>
+          <t>23,54; 55,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,58; 26,06</t>
+          <t>17,87; 25,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39,01; 48,79</t>
+          <t>39,07; 49,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,72; 36,03</t>
+          <t>27,21; 36,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,05; 45,44</t>
+          <t>27,93; 45,79</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,75; 23,9</t>
+          <t>14,03; 23,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,73; 38,73</t>
+          <t>27,14; 38,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,42; 29,12</t>
+          <t>18,74; 29,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38,09; 48,63</t>
+          <t>38,02; 48,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,39; 42,28</t>
+          <t>29,97; 40,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,91; 51,9</t>
+          <t>40,15; 52,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,48; 40,69</t>
+          <t>29,0; 40,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44,75; 55,24</t>
+          <t>44,16; 54,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,48; 30,95</t>
+          <t>23,91; 30,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35,11; 43,68</t>
+          <t>35,38; 43,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25,69; 33,67</t>
+          <t>25,79; 33,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42,4; 49,73</t>
+          <t>42,51; 49,94</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,47; 22,83</t>
+          <t>16,33; 22,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,4; 30,58</t>
+          <t>22,94; 30,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,58; 25,35</t>
+          <t>18,47; 25,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35,33; 44,6</t>
+          <t>35,1; 43,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,95; 33,19</t>
+          <t>26,37; 33,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,79; 43,49</t>
+          <t>36,08; 43,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,02; 35,91</t>
+          <t>29,24; 36,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60,79; 84,75</t>
+          <t>60,52; 85,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,15; 27,13</t>
+          <t>22,19; 27,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,74; 36,05</t>
+          <t>30,75; 36,11</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,75; 29,74</t>
+          <t>25,08; 30,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,21; 74,53</t>
+          <t>49,86; 72,27</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,22; 28,43</t>
+          <t>22,14; 28,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,97; 22,82</t>
+          <t>16,7; 22,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,31; 29,9</t>
+          <t>23,48; 29,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,66; 28,25</t>
+          <t>9,26; 28,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,78; 41,15</t>
+          <t>33,84; 40,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,61; 33,09</t>
+          <t>26,73; 33,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,87; 38,96</t>
+          <t>32,03; 38,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>34,81; 41,14</t>
+          <t>34,89; 40,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,05; 33,92</t>
+          <t>28,99; 33,68</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,96; 27,39</t>
+          <t>22,6; 27,18</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29,0; 33,74</t>
+          <t>28,65; 33,46</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,61; 33,4</t>
+          <t>17,03; 33,62</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,39; 21,02</t>
+          <t>18,45; 21,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22,97; 25,93</t>
+          <t>22,82; 25,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22,51; 25,31</t>
+          <t>22,39; 25,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24,15; 33,44</t>
+          <t>23,27; 33,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,94; 35,34</t>
+          <t>31,94; 35,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,1; 40,54</t>
+          <t>37,09; 40,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,45; 37,77</t>
+          <t>34,58; 37,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>45,36; 58,39</t>
+          <t>45,39; 58,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,53; 27,87</t>
+          <t>25,7; 27,75</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30,5; 32,73</t>
+          <t>30,49; 32,67</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28,93; 31,19</t>
+          <t>28,88; 31,12</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>36,37; 46,04</t>
+          <t>36,6; 45,61</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas</t>
+          <t>Población con dos o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39298; 63561</t>
+          <t>39183; 65110</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53758; 84006</t>
+          <t>53483; 83031</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57294; 87911</t>
+          <t>58351; 89552</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70800; 106060</t>
+          <t>71545; 106669</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53881; 82166</t>
+          <t>53228; 82256</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100726; 135286</t>
+          <t>100894; 138408</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>103247; 137458</t>
+          <t>102617; 137049</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>85564; 111189</t>
+          <t>84946; 110735</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>99358; 135959</t>
+          <t>98128; 136086</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164933; 211413</t>
+          <t>163008; 209520</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>169038; 215202</t>
+          <t>169548; 214507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>163392; 209946</t>
+          <t>164863; 207500</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72027; 107118</t>
+          <t>74655; 109089</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87405; 127303</t>
+          <t>89292; 129528</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90874; 127070</t>
+          <t>92895; 130923</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>112278; 159580</t>
+          <t>110483; 156644</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>182474; 226360</t>
+          <t>182952; 225764</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>160879; 203063</t>
+          <t>157744; 205380</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>161832; 207069</t>
+          <t>163120; 206654</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>184554; 224393</t>
+          <t>187313; 225950</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>264803; 323000</t>
+          <t>264552; 320826</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255527; 320153</t>
+          <t>259519; 316969</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>263729; 325609</t>
+          <t>265612; 323069</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>308052; 372684</t>
+          <t>307367; 369969</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41126; 66871</t>
+          <t>41353; 68825</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74424; 107864</t>
+          <t>74361; 108434</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47464; 74894</t>
+          <t>48176; 74366</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97132; 129783</t>
+          <t>97523; 127759</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>86511; 120595</t>
+          <t>85260; 119191</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>106803; 142634</t>
+          <t>106884; 144123</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90242; 124903</t>
+          <t>91977; 126079</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>147275; 179502</t>
+          <t>148408; 179191</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135959; 178271</t>
+          <t>134242; 177124</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>189232; 239567</t>
+          <t>193587; 242926</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>147146; 190588</t>
+          <t>145839; 191269</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>254751; 299915</t>
+          <t>252093; 296585</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58868; 89852</t>
+          <t>62261; 91759</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72833; 107554</t>
+          <t>71767; 106221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>89975; 127694</t>
+          <t>88904; 124347</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93480; 132762</t>
+          <t>92152; 130104</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>97820; 133707</t>
+          <t>96746; 131640</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>151565; 192459</t>
+          <t>151677; 191314</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>146307; 186235</t>
+          <t>145152; 185617</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>197584; 337274</t>
+          <t>196773; 340899</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>165990; 210235</t>
+          <t>166149; 212916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>233212; 287640</t>
+          <t>231869; 289533</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>244016; 299234</t>
+          <t>245760; 303180</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>305431; 491334</t>
+          <t>306728; 471817</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17921; 36772</t>
+          <t>17286; 35910</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47593; 74573</t>
+          <t>46530; 73917</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36575; 61004</t>
+          <t>36601; 61142</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49733; 69599</t>
+          <t>50290; 70312</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>49797; 78449</t>
+          <t>50433; 77257</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>115747; 143806</t>
+          <t>115798; 146001</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74072; 102126</t>
+          <t>75582; 102300</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>57763; 142637</t>
+          <t>60919; 143242</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>72247; 107106</t>
+          <t>73424; 106286</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>168624; 210860</t>
+          <t>168874; 213575</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>119149; 154866</t>
+          <t>116938; 155133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>113963; 198790</t>
+          <t>122208; 200356</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39943; 64728</t>
+          <t>38004; 62969</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>75962; 106117</t>
+          <t>74364; 105972</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48454; 76634</t>
+          <t>49304; 77727</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>102700; 131132</t>
+          <t>102524; 130727</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>84534; 117588</t>
+          <t>83348; 113748</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>111770; 145333</t>
+          <t>112446; 145997</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77784; 111129</t>
+          <t>79191; 110781</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>115033; 142002</t>
+          <t>113522; 140881</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>128873; 169884</t>
+          <t>131257; 170045</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>194532; 242009</t>
+          <t>196033; 240862</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>137750; 180571</t>
+          <t>138291; 179973</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>223326; 261907</t>
+          <t>223871; 263052</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>101322; 140427</t>
+          <t>100410; 139277</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>155123; 202684</t>
+          <t>152056; 200560</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121973; 166439</t>
+          <t>121237; 165631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>220537; 278424</t>
+          <t>219135; 274158</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>165590; 211827</t>
+          <t>168330; 213260</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>248348; 301750</t>
+          <t>250325; 300936</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>200592; 248238</t>
+          <t>202166; 252414</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>516307; 719717</t>
+          <t>514008; 726492</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>277581; 340039</t>
+          <t>278139; 339212</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>417019; 489022</t>
+          <t>417119; 489857</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>333638; 400870</t>
+          <t>338031; 408012</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>739848; 1098214</t>
+          <t>734648; 1064908</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>165262; 211426</t>
+          <t>164641; 208920</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>132221; 177755</t>
+          <t>130118; 174944</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>181526; 232795</t>
+          <t>182799; 231993</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>80471; 262365</t>
+          <t>85975; 263275</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>264696; 322414</t>
+          <t>265108; 320474</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>219261; 272602</t>
+          <t>220195; 271922</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>263302; 321863</t>
+          <t>264606; 321330</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>249865; 295282</t>
+          <t>250450; 292902</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>443629; 518115</t>
+          <t>442784; 514339</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>368104; 438989</t>
+          <t>362265; 435757</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>465303; 541476</t>
+          <t>459689; 536956</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>289973; 549943</t>
+          <t>280408; 553534</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>602418; 688582</t>
+          <t>604686; 692536</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>787129; 888717</t>
+          <t>782057; 883353</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>764151; 859191</t>
+          <t>759917; 856995</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>835717; 1156801</t>
+          <t>805141; 1153971</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1079246; 1194125</t>
+          <t>1079368; 1189882</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1320215; 1442583</t>
+          <t>1319650; 1442411</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1220979; 1338743</t>
+          <t>1225763; 1344973</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1683891; 2167780</t>
+          <t>1684866; 2187398</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1699278; 1855089</t>
+          <t>1710286; 1847148</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2130636; 2286226</t>
+          <t>2129607; 2282063</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2007492; 2164548</t>
+          <t>2004080; 2159177</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2608595; 3302182</t>
+          <t>2625165; 3271032</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,35; 23,85</t>
+          <t>13,69; 23,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 28,17</t>
+          <t>18,35; 27,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,86; 30,48</t>
+          <t>19,79; 30,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,97; 34,25</t>
+          <t>22,57; 32,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,41; 31,54</t>
+          <t>20,5; 31,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,12; 48,18</t>
+          <t>34,98; 47,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,54; 47,47</t>
+          <t>35,95; 47,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,33; 38,23</t>
+          <t>28,69; 36,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,38; 25,49</t>
+          <t>18,38; 25,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,01; 36,0</t>
+          <t>28,04; 36,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,11; 36,83</t>
+          <t>29,47; 37,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,43; 34,52</t>
+          <t>27,09; 33,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 22,12</t>
+          <t>14,8; 21,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,66; 25,62</t>
+          <t>16,98; 25,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 26,05</t>
+          <t>18,23; 25,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,31; 30,22</t>
+          <t>21,79; 30,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,3; 44,8</t>
+          <t>36,32; 45,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,12; 39,21</t>
+          <t>30,33; 38,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,18; 39,51</t>
+          <t>31,12; 39,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,37; 43,88</t>
+          <t>36,1; 43,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,53; 32,18</t>
+          <t>26,73; 32,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,21; 30,79</t>
+          <t>24,85; 31,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,9; 31,5</t>
+          <t>25,72; 31,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,74; 35,8</t>
+          <t>30,24; 36,3</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,97; 21,59</t>
+          <t>12,55; 20,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,95; 33,46</t>
+          <t>23,3; 33,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,12; 23,34</t>
+          <t>15,56; 23,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,86; 40,42</t>
+          <t>30,91; 40,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,42; 35,54</t>
+          <t>25,97; 35,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,34; 42,26</t>
+          <t>31,11; 41,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,35; 37,49</t>
+          <t>27,15; 37,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,51; 51,33</t>
+          <t>42,52; 51,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,52; 27,07</t>
+          <t>20,6; 27,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,11; 36,53</t>
+          <t>28,78; 36,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,27; 29,21</t>
+          <t>22,34; 29,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,9; 44,59</t>
+          <t>38,85; 45,29</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,36; 25,58</t>
+          <t>16,65; 25,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,19; 28,4</t>
+          <t>19,23; 28,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,03; 33,61</t>
+          <t>24,32; 34,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,48; 41,63</t>
+          <t>27,4; 40,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,05; 35,44</t>
+          <t>26,46; 35,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,0; 49,19</t>
+          <t>38,96; 49,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,48; 47,93</t>
+          <t>37,83; 48,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,36; 71,66</t>
+          <t>42,52; 51,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,76; 29,16</t>
+          <t>22,98; 29,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,39; 37,95</t>
+          <t>30,79; 37,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32,45; 40,04</t>
+          <t>32,56; 39,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38,91; 59,85</t>
+          <t>36,78; 44,0</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,5; 17,66</t>
+          <t>8,84; 18,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,88; 34,76</t>
+          <t>22,2; 35,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,33; 28,95</t>
+          <t>17,91; 28,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,14; 39,34</t>
+          <t>25,87; 36,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,29; 37,2</t>
+          <t>24,62; 37,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,73; 66,49</t>
+          <t>52,5; 65,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,58; 46,8</t>
+          <t>33,98; 47,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,54; 55,35</t>
+          <t>47,32; 56,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,87; 25,86</t>
+          <t>17,27; 25,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39,07; 49,41</t>
+          <t>38,65; 48,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,21; 36,09</t>
+          <t>27,67; 36,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,93; 45,79</t>
+          <t>38,57; 46,01</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,03; 23,25</t>
+          <t>14,43; 23,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,14; 38,68</t>
+          <t>27,71; 38,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,74; 29,54</t>
+          <t>19,07; 29,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38,02; 48,48</t>
+          <t>37,64; 48,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,97; 40,9</t>
+          <t>30,15; 41,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,15; 52,14</t>
+          <t>39,91; 51,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,0; 40,56</t>
+          <t>28,99; 40,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44,16; 54,81</t>
+          <t>44,48; 54,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,91; 30,98</t>
+          <t>22,96; 30,57</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35,38; 43,48</t>
+          <t>34,92; 43,38</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25,79; 33,56</t>
+          <t>25,49; 33,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42,51; 49,94</t>
+          <t>42,36; 49,44</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>51,52%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,33; 22,65</t>
+          <t>16,33; 22,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,94; 30,26</t>
+          <t>23,18; 30,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,47; 25,23</t>
+          <t>18,61; 25,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35,1; 43,92</t>
+          <t>36,05; 44,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,37; 33,41</t>
+          <t>26,42; 33,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,08; 43,37</t>
+          <t>36,04; 43,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,24; 36,51</t>
+          <t>28,73; 35,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60,52; 85,54</t>
+          <t>58,68; 65,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,19; 27,07</t>
+          <t>22,22; 26,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,75; 36,11</t>
+          <t>30,56; 35,91</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25,08; 30,27</t>
+          <t>24,9; 29,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,86; 72,27</t>
+          <t>48,86; 54,46</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,14; 28,09</t>
+          <t>22,19; 28,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,7; 22,45</t>
+          <t>16,78; 22,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,48; 29,8</t>
+          <t>23,52; 30,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,26; 28,35</t>
+          <t>23,28; 29,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,84; 40,9</t>
+          <t>33,93; 41,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,73; 33,01</t>
+          <t>26,53; 33,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,03; 38,89</t>
+          <t>31,99; 39,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>34,89; 40,81</t>
+          <t>34,38; 40,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28,99; 33,68</t>
+          <t>28,94; 33,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,6; 27,18</t>
+          <t>22,87; 27,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28,65; 33,46</t>
+          <t>28,91; 33,56</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,03; 33,62</t>
+          <t>29,75; 34,01</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,45; 21,14</t>
+          <t>18,38; 21,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22,82; 25,78</t>
+          <t>22,79; 25,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22,39; 25,25</t>
+          <t>22,38; 25,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23,27; 33,35</t>
+          <t>30,72; 34,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,94; 35,21</t>
+          <t>31,92; 35,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,09; 40,54</t>
+          <t>37,14; 40,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,58; 37,94</t>
+          <t>34,38; 37,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>45,39; 58,92</t>
+          <t>44,79; 47,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,7; 27,75</t>
+          <t>25,72; 27,96</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30,49; 32,67</t>
+          <t>30,53; 32,86</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28,88; 31,12</t>
+          <t>28,96; 31,24</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>36,6; 45,61</t>
+          <t>38,18; 40,53</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87760</t>
+          <t>87268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>97808</t>
+          <t>103917</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>185567</t>
+          <t>191185</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39183; 65110</t>
+          <t>37383; 63702</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53483; 83031</t>
+          <t>54091; 82204</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58351; 89552</t>
+          <t>58126; 88503</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71545; 106669</t>
+          <t>71979; 103635</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53228; 82256</t>
+          <t>53478; 82223</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100894; 138408</t>
+          <t>100491; 136254</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>102617; 137049</t>
+          <t>103796; 137092</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84946; 110735</t>
+          <t>90663; 116306</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>98128; 136086</t>
+          <t>98121; 137589</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>163008; 209520</t>
+          <t>163165; 210428</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>169548; 214507</t>
+          <t>171633; 215685</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>164863; 207500</t>
+          <t>171983; 211049</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133518</t>
+          <t>138156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>205369</t>
+          <t>216973</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>338886</t>
+          <t>355129</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74655; 109089</t>
+          <t>72971; 107272</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89292; 129528</t>
+          <t>85831; 126406</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92895; 130923</t>
+          <t>91641; 128510</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>110483; 156644</t>
+          <t>115606; 162810</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>182952; 225764</t>
+          <t>183036; 226862</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>157744; 205380</t>
+          <t>158863; 203622</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>163120; 206654</t>
+          <t>162760; 207068</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>187313; 225950</t>
+          <t>197312; 237968</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>264552; 320826</t>
+          <t>266497; 322685</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>259519; 316969</t>
+          <t>255829; 322158</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>265612; 323069</t>
+          <t>263822; 324757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>307367; 369969</t>
+          <t>325705; 390979</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112273</t>
+          <t>113388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>163465</t>
+          <t>168565</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>275738</t>
+          <t>281953</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41353; 68825</t>
+          <t>40003; 66886</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74361; 108434</t>
+          <t>75502; 108158</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48176; 74366</t>
+          <t>49572; 74534</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97523; 127759</t>
+          <t>97661; 129210</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>85260; 119191</t>
+          <t>87099; 119474</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>106884; 144123</t>
+          <t>106108; 142161</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91977; 126079</t>
+          <t>91320; 126670</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>148408; 179191</t>
+          <t>151541; 183490</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>134242; 177124</t>
+          <t>134780; 180042</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>193587; 242926</t>
+          <t>191384; 241858</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145839; 191269</t>
+          <t>146293; 192549</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>252093; 296585</t>
+          <t>261248; 304514</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111584</t>
+          <t>123671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>250516</t>
+          <t>199328</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>362099</t>
+          <t>323000</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62261; 91759</t>
+          <t>59707; 89906</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71767; 106221</t>
+          <t>71908; 105398</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88904; 124347</t>
+          <t>89973; 126394</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92152; 130104</t>
+          <t>102242; 149713</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>96746; 131640</t>
+          <t>98291; 131824</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>151677; 191314</t>
+          <t>151546; 191667</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>145152; 185617</t>
+          <t>146517; 188220</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>196773; 340899</t>
+          <t>179405; 218862</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166149; 212916</t>
+          <t>167764; 213402</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>231869; 289533</t>
+          <t>234912; 286845</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>245760; 303180</t>
+          <t>246586; 302089</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>306728; 471817</t>
+          <t>292418; 349884</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59513</t>
+          <t>64127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>112999</t>
+          <t>119015</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>172512</t>
+          <t>183141</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17286; 35910</t>
+          <t>17973; 37463</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46530; 73917</t>
+          <t>47209; 75070</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36601; 61142</t>
+          <t>37823; 60958</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50290; 70312</t>
+          <t>53209; 74852</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50433; 77257</t>
+          <t>51123; 78863</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>115798; 146001</t>
+          <t>115294; 143078</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75582; 102300</t>
+          <t>74265; 103366</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>60919; 143242</t>
+          <t>108319; 129918</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73424; 106286</t>
+          <t>70988; 106320</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>168874; 213575</t>
+          <t>167066; 208290</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>116938; 155133</t>
+          <t>118940; 156637</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>122208; 200356</t>
+          <t>167615; 199942</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116316</t>
+          <t>115244</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>127028</t>
+          <t>129910</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>243344</t>
+          <t>245154</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38004; 62969</t>
+          <t>39084; 63770</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>74364; 105972</t>
+          <t>75913; 106486</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49304; 77727</t>
+          <t>50176; 77746</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>102524; 130727</t>
+          <t>101885; 130452</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>83348; 113748</t>
+          <t>83864; 114727</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>112446; 145997</t>
+          <t>111764; 144696</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79191; 110781</t>
+          <t>79167; 109990</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>113522; 140881</t>
+          <t>117325; 144036</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>131257; 170045</t>
+          <t>126032; 167822</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>196033; 240862</t>
+          <t>193472; 240354</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>138291; 179973</t>
+          <t>136707; 181051</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>223871; 263052</t>
+          <t>226413; 264231</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247221</t>
+          <t>289551</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>602836</t>
+          <t>478989</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>850057</t>
+          <t>768539</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>100410; 139277</t>
+          <t>100460; 140796</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>152056; 200560</t>
+          <t>153650; 201107</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121237; 165631</t>
+          <t>122207; 164636</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>219135; 274158</t>
+          <t>259472; 319613</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>168330; 213260</t>
+          <t>168634; 213782</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>250325; 300936</t>
+          <t>250085; 301182</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>202166; 252414</t>
+          <t>198643; 248381</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>514008; 726492</t>
+          <t>453046; 505314</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>278139; 339212</t>
+          <t>278494; 337502</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>417119; 489857</t>
+          <t>414596; 487197</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>338031; 408012</t>
+          <t>335626; 403114</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>734648; 1064908</t>
+          <t>728908; 812430</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186494</t>
+          <t>209413</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>271949</t>
+          <t>307446</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>458443</t>
+          <t>516859</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>164641; 208920</t>
+          <t>165035; 212192</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>130118; 174944</t>
+          <t>130696; 177800</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>182799; 231993</t>
+          <t>183121; 234476</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>85975; 263275</t>
+          <t>185829; 233599</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>265108; 320474</t>
+          <t>265868; 321857</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>220195; 271922</t>
+          <t>218593; 272260</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>264606; 321330</t>
+          <t>264254; 322735</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>250450; 292902</t>
+          <t>285825; 332767</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>442784; 514339</t>
+          <t>441934; 516331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>362265; 435757</t>
+          <t>366626; 436011</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>459689; 536956</t>
+          <t>463881; 538496</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>280408; 553534</t>
+          <t>484801; 554120</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1054679</t>
+          <t>1140819</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1831969</t>
+          <t>1724142</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2886648</t>
+          <t>2864962</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>604686; 692536</t>
+          <t>602391; 693201</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>782057; 883353</t>
+          <t>780825; 885096</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>759917; 856995</t>
+          <t>759512; 861636</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>805141; 1153971</t>
+          <t>1085220; 1205055</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1079368; 1189882</t>
+          <t>1078673; 1189146</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1319650; 1442411</t>
+          <t>1321643; 1434835</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1225763; 1344973</t>
+          <t>1218532; 1342725</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1684866; 2187398</t>
+          <t>1673647; 1779174</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1710286; 1847148</t>
+          <t>1711947; 1860969</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2129607; 2282063</t>
+          <t>2132730; 2295311</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2004080; 2159177</t>
+          <t>2009158; 2167617</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2625165; 3271032</t>
+          <t>2775215; 2946273</t>
         </is>
       </c>
     </row>
